--- a/03_Outputs/all/03_DS/ds_idx9_infnin.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx9_infnin.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.6440354634381583</v>
+        <v>0.6440354634381613</v>
       </c>
       <c r="D2">
-        <v>-1.589065073782211</v>
+        <v>-1.589065073782208</v>
       </c>
       <c r="E2">
-        <v>-0.2074231325988814</v>
+        <v>-0.2074231325988821</v>
       </c>
       <c r="F2">
-        <v>0.1463120181419612</v>
+        <v>0.1463120181419613</v>
       </c>
       <c r="G2">
-        <v>0.6460898367421346</v>
+        <v>0.6460898367421357</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.7964145680207588</v>
+        <v>-0.7964145680207596</v>
       </c>
       <c r="D3">
-        <v>0.3729476459537691</v>
+        <v>0.3729476459537689</v>
       </c>
       <c r="E3">
-        <v>0.4351619698712086</v>
+        <v>0.4351619698712099</v>
       </c>
       <c r="F3">
-        <v>0.9718196714020111</v>
+        <v>0.9718196714020101</v>
       </c>
       <c r="G3">
-        <v>0.3578200839858441</v>
+        <v>0.3578200839858464</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>-2.563025820137726</v>
+        <v>-2.563025820137729</v>
       </c>
       <c r="D4">
-        <v>1.574125365080811</v>
+        <v>1.574125365080804</v>
       </c>
       <c r="E4">
-        <v>1.731635704875835</v>
+        <v>1.731635704875833</v>
       </c>
       <c r="F4">
-        <v>-0.4386203758052918</v>
+        <v>-0.4386203758052939</v>
       </c>
       <c r="G4">
-        <v>-0.1050771032811558</v>
+        <v>-0.1050771032811581</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-1.871716625033967</v>
+        <v>-1.871716625033968</v>
       </c>
       <c r="D5">
-        <v>0.4472841061840575</v>
+        <v>0.4472841061840547</v>
       </c>
       <c r="E5">
-        <v>0.9060537829427787</v>
+        <v>0.9060537829427794</v>
       </c>
       <c r="F5">
-        <v>2.014417855896632</v>
+        <v>2.014417855896633</v>
       </c>
       <c r="G5">
-        <v>-0.8166408846202465</v>
+        <v>-0.8166408846202433</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.6350370387977915</v>
+        <v>-0.6350370387977903</v>
       </c>
       <c r="D6">
-        <v>-0.24891732984293</v>
+        <v>-0.2489173298429299</v>
       </c>
       <c r="E6">
-        <v>0.0496221643034214</v>
+        <v>0.04962216430342112</v>
       </c>
       <c r="F6">
-        <v>-0.09029552093979712</v>
+        <v>-0.09029552093979984</v>
       </c>
       <c r="G6">
-        <v>0.937576437559506</v>
+        <v>0.9375764375595029</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.8041902982700311</v>
+        <v>-0.8041902982700334</v>
       </c>
       <c r="D7">
-        <v>1.305268141780797</v>
+        <v>1.305268141780794</v>
       </c>
       <c r="E7">
-        <v>0.2830214962035527</v>
+        <v>0.2830214962035539</v>
       </c>
       <c r="F7">
-        <v>0.5189029175536063</v>
+        <v>0.5189029175536054</v>
       </c>
       <c r="G7">
-        <v>-0.6535054600361988</v>
+        <v>-0.6535054600361978</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.122085324228003</v>
+        <v>-0.1220853242280027</v>
       </c>
       <c r="D8">
-        <v>-0.1563689151158641</v>
+        <v>-0.1563689151158631</v>
       </c>
       <c r="E8">
-        <v>-0.6012238453173097</v>
+        <v>-0.6012238453173088</v>
       </c>
       <c r="F8">
-        <v>-0.4199117093812234</v>
+        <v>-0.4199117093812248</v>
       </c>
       <c r="G8">
-        <v>0.6583384593367164</v>
+        <v>0.6583384593367174</v>
       </c>
     </row>
     <row r="9">
@@ -595,13 +595,13 @@
         <v>-0.8073281948808155</v>
       </c>
       <c r="D9">
-        <v>0.3452110787304126</v>
+        <v>0.3452110787304079</v>
       </c>
       <c r="E9">
-        <v>-0.4820345173486415</v>
+        <v>-0.4820345173486436</v>
       </c>
       <c r="F9">
-        <v>-2.782736316157443</v>
+        <v>-2.782736316157441</v>
       </c>
       <c r="G9">
         <v>-0.6171673807830004</v>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.955360888989223</v>
+        <v>-0.9553608889892243</v>
       </c>
       <c r="D10">
-        <v>0.8116052006762148</v>
+        <v>0.811605200676214</v>
       </c>
       <c r="E10">
-        <v>0.023194345911996</v>
+        <v>0.02319434591199671</v>
       </c>
       <c r="F10">
-        <v>-0.4201678122487269</v>
+        <v>-0.4201678122487303</v>
       </c>
       <c r="G10">
-        <v>0.9003383672242584</v>
+        <v>0.9003383672242622</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.8724417350981567</v>
+        <v>-0.8724417350981571</v>
       </c>
       <c r="D11">
-        <v>0.3814400190675403</v>
+        <v>0.3814400190675394</v>
       </c>
       <c r="E11">
-        <v>0.04284289158675526</v>
+        <v>0.04284289158675524</v>
       </c>
       <c r="F11">
-        <v>-0.04650224913012842</v>
+        <v>-0.04650224913012868</v>
       </c>
       <c r="G11">
-        <v>0.278878385030683</v>
+        <v>0.2788783850306865</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>1.051560166263282</v>
+        <v>1.051560166263283</v>
       </c>
       <c r="D12">
-        <v>0.1688472540393597</v>
+        <v>0.1688472540393601</v>
       </c>
       <c r="E12">
-        <v>0.1271918310468931</v>
+        <v>0.1271918310468925</v>
       </c>
       <c r="F12">
-        <v>-1.225761454984204</v>
+        <v>-1.225761454984206</v>
       </c>
       <c r="G12">
-        <v>0.3181293467627651</v>
+        <v>0.3181293467627637</v>
       </c>
     </row>
     <row r="13">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.08998753424057807</v>
+        <v>0.08998753424057823</v>
       </c>
       <c r="D13">
-        <v>0.04643351815108269</v>
+        <v>0.04643351815108143</v>
       </c>
       <c r="E13">
-        <v>-0.9253191250627766</v>
+        <v>-0.9253191250627768</v>
       </c>
       <c r="F13">
-        <v>-1.2282278232611</v>
+        <v>-1.228227823261095</v>
       </c>
       <c r="G13">
         <v>-1.084755105614476</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.3294542049734508</v>
+        <v>0.3294542049734528</v>
       </c>
       <c r="D14">
-        <v>-0.8228993151671695</v>
+        <v>-0.822899315167169</v>
       </c>
       <c r="E14">
-        <v>0.8877022675803888</v>
+        <v>0.8877022675803882</v>
       </c>
       <c r="F14">
-        <v>0.5558834699117967</v>
+        <v>0.5558834699117975</v>
       </c>
       <c r="G14">
-        <v>0.2545436036601519</v>
+        <v>0.2545436036601527</v>
       </c>
     </row>
     <row r="15">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.03803972575938099</v>
+        <v>-0.03803972575938144</v>
       </c>
       <c r="D15">
-        <v>0.3446716573918883</v>
+        <v>0.3446716573918853</v>
       </c>
       <c r="E15">
-        <v>0.9042679122576284</v>
+        <v>0.9042679122576271</v>
       </c>
       <c r="F15">
-        <v>-0.7970078679182343</v>
+        <v>-0.7970078679182317</v>
       </c>
       <c r="G15">
         <v>-1.004237470201675</v>
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.2797900359531141</v>
+        <v>-0.2797900359531146</v>
       </c>
       <c r="D16">
-        <v>0.03284092536189227</v>
+        <v>0.03284092536189105</v>
       </c>
       <c r="E16">
-        <v>1.227670611256162</v>
+        <v>1.22767061125616</v>
       </c>
       <c r="F16">
-        <v>-0.6555134023223677</v>
+        <v>-0.6555134023223692</v>
       </c>
       <c r="G16">
-        <v>1.159080382007358</v>
+        <v>1.159080382007357</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>-3.9110232130538</v>
+        <v>-3.911023213053805</v>
       </c>
       <c r="D17">
-        <v>2.404397532132573</v>
+        <v>2.404397532132569</v>
       </c>
       <c r="E17">
-        <v>-0.5428727692051479</v>
+        <v>-0.5428727692051425</v>
       </c>
       <c r="F17">
-        <v>1.815613394888947</v>
+        <v>1.81561339488895</v>
       </c>
       <c r="G17">
-        <v>-0.3450208435149921</v>
+        <v>-0.3450208435149865</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.7524434261230541</v>
+        <v>-0.752443426123053</v>
       </c>
       <c r="D18">
-        <v>-0.6625861193775248</v>
+        <v>-0.6625861193775247</v>
       </c>
       <c r="E18">
-        <v>-0.2944262406846203</v>
+        <v>-0.2944262406846199</v>
       </c>
       <c r="F18">
-        <v>0.6261677128617714</v>
+        <v>0.6261677128617723</v>
       </c>
       <c r="G18">
-        <v>0.1556401571221399</v>
+        <v>0.1556401571221417</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>-1.470978269510069</v>
+        <v>-1.47097826951007</v>
       </c>
       <c r="D19">
-        <v>0.5026622310044628</v>
+        <v>0.5026622310044577</v>
       </c>
       <c r="E19">
-        <v>0.9165819756742207</v>
+        <v>0.9165819756742173</v>
       </c>
       <c r="F19">
-        <v>-1.453910615335701</v>
+        <v>-1.4539106153357</v>
       </c>
       <c r="G19">
-        <v>-0.693031371933166</v>
+        <v>-0.6930313719331672</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.444814741124236</v>
+        <v>0.4448147411242384</v>
       </c>
       <c r="D20">
-        <v>-1.005484851972178</v>
+        <v>-1.005484851972175</v>
       </c>
       <c r="E20">
-        <v>-0.7404368159498722</v>
+        <v>-0.7404368159498717</v>
       </c>
       <c r="F20">
-        <v>0.299930170713568</v>
+        <v>0.2999301707135668</v>
       </c>
       <c r="G20">
-        <v>0.7434406634954146</v>
+        <v>0.7434406634954169</v>
       </c>
     </row>
     <row r="21">
@@ -919,13 +919,13 @@
         <v>-0.2485641227133562</v>
       </c>
       <c r="D21">
-        <v>0.9990251224513498</v>
+        <v>0.999025122451355</v>
       </c>
       <c r="E21">
-        <v>-2.485117791213728</v>
+        <v>-2.485117791213724</v>
       </c>
       <c r="F21">
-        <v>0.3896407028438612</v>
+        <v>0.3896407028438543</v>
       </c>
       <c r="G21">
         <v>2.339113615972523</v>
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.2136369542821547</v>
+        <v>-0.213636954282154</v>
       </c>
       <c r="D22">
-        <v>0.3142993233932902</v>
+        <v>0.3142993233932879</v>
       </c>
       <c r="E22">
-        <v>1.854249832576757</v>
+        <v>1.854249832576754</v>
       </c>
       <c r="F22">
-        <v>-0.6750075309918896</v>
+        <v>-0.6750075309918926</v>
       </c>
       <c r="G22">
-        <v>0.7640989759413572</v>
+        <v>0.7640989759413535</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.3349882675870542</v>
+        <v>0.3349882675870546</v>
       </c>
       <c r="D23">
-        <v>-0.1856469920854641</v>
+        <v>-0.1856469920854604</v>
       </c>
       <c r="E23">
-        <v>-2.203256204640164</v>
+        <v>-2.20325620464016</v>
       </c>
       <c r="F23">
-        <v>0.3534277788316411</v>
+        <v>0.3534277788316396</v>
       </c>
       <c r="G23">
-        <v>0.7773661160907518</v>
+        <v>0.777366116090757</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-1.207829542536083</v>
+        <v>-1.207829542536085</v>
       </c>
       <c r="D24">
-        <v>0.8489973036341172</v>
+        <v>0.8489973036341151</v>
       </c>
       <c r="E24">
-        <v>0.6365083107210818</v>
+        <v>0.6365083107210819</v>
       </c>
       <c r="F24">
-        <v>0.1646698341077856</v>
+        <v>0.1646698341077849</v>
       </c>
       <c r="G24">
-        <v>0.1554545202192713</v>
+        <v>0.1554545202192729</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.4316356711399408</v>
+        <v>0.4316356711399355</v>
       </c>
       <c r="D25">
-        <v>1.242789765315105</v>
+        <v>1.242789765315103</v>
       </c>
       <c r="E25">
-        <v>-0.9176480153960894</v>
+        <v>-0.9176480153960891</v>
       </c>
       <c r="F25">
-        <v>-0.2177943961807487</v>
+        <v>-0.2177943961807431</v>
       </c>
       <c r="G25">
-        <v>-1.720798928435247</v>
+        <v>-1.720798928435246</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>1.48438986071143</v>
+        <v>1.484389860711427</v>
       </c>
       <c r="D26">
         <v>1.397765618524132</v>
       </c>
       <c r="E26">
-        <v>-0.9128524015885136</v>
+        <v>-0.9128524015885123</v>
       </c>
       <c r="F26">
         <v>-1.211777228222488</v>
       </c>
       <c r="G26">
-        <v>-0.3460212050554677</v>
+        <v>-0.3460212050554681</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.6197498491626136</v>
+        <v>-0.6197498491626149</v>
       </c>
       <c r="D27">
-        <v>0.703726970839626</v>
+        <v>0.7037269708396233</v>
       </c>
       <c r="E27">
-        <v>0.07293177977501002</v>
+        <v>0.07293177977501082</v>
       </c>
       <c r="F27">
-        <v>-0.5982997106593195</v>
+        <v>-0.5982997106593158</v>
       </c>
       <c r="G27">
-        <v>-0.826665491900883</v>
+        <v>-0.826665491900884</v>
       </c>
     </row>
     <row r="28">
@@ -1105,16 +1105,16 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.7303324292953778</v>
+        <v>0.7303324292953814</v>
       </c>
       <c r="D28">
-        <v>-1.75929880473372</v>
+        <v>-1.759298804733717</v>
       </c>
       <c r="E28">
-        <v>-0.4589716122852122</v>
+        <v>-0.4589716122852135</v>
       </c>
       <c r="F28">
-        <v>-0.2880300155394298</v>
+        <v>-0.28803001553943</v>
       </c>
       <c r="G28">
         <v>0.5213608516677561</v>
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-1.635883333325805</v>
+        <v>-1.635883333325808</v>
       </c>
       <c r="D29">
-        <v>1.225111148060064</v>
+        <v>1.225111148060061</v>
       </c>
       <c r="E29">
-        <v>1.431554156050273</v>
+        <v>1.431554156050272</v>
       </c>
       <c r="F29">
-        <v>0.2218452422287802</v>
+        <v>0.2218452422287747</v>
       </c>
       <c r="G29">
-        <v>0.9066253256947673</v>
+        <v>0.9066253256947658</v>
       </c>
     </row>
     <row r="30">
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.7436340776245188</v>
+        <v>0.7436340776245189</v>
       </c>
       <c r="D30">
-        <v>1.055458024151056</v>
+        <v>1.055458024151061</v>
       </c>
       <c r="E30">
-        <v>-0.1110293102565399</v>
+        <v>-0.1110293102565373</v>
       </c>
       <c r="F30">
-        <v>1.077244546254401</v>
+        <v>1.077244546254394</v>
       </c>
       <c r="G30">
         <v>2.226192592260484</v>
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.6337350009653435</v>
+        <v>-0.6337350009653462</v>
       </c>
       <c r="D31">
-        <v>1.77806129589379</v>
+        <v>1.778061295893789</v>
       </c>
       <c r="E31">
-        <v>-1.936612547864512</v>
+        <v>-1.936612547864509</v>
       </c>
       <c r="F31">
-        <v>0.005368048913350816</v>
+        <v>0.005368048913355267</v>
       </c>
       <c r="G31">
-        <v>-1.755792711520687</v>
+        <v>-1.755792711520683</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.99652573845078</v>
+        <v>-0.9965257384507817</v>
       </c>
       <c r="D32">
-        <v>0.9996197311986239</v>
+        <v>0.9996197311986212</v>
       </c>
       <c r="E32">
-        <v>0.0648686501343527</v>
+        <v>0.06486865013435586</v>
       </c>
       <c r="F32">
-        <v>1.62193818376627</v>
+        <v>1.621938183766274</v>
       </c>
       <c r="G32">
-        <v>-1.755550878380532</v>
+        <v>-1.755550878380526</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.8012192389889236</v>
+        <v>0.8012192389889253</v>
       </c>
       <c r="D33">
-        <v>-0.8864600894330816</v>
+        <v>-0.8864600894330803</v>
       </c>
       <c r="E33">
-        <v>1.018706831248281</v>
+        <v>1.01870683124828</v>
       </c>
       <c r="F33">
-        <v>1.027997064587091</v>
+        <v>1.02799706458709</v>
       </c>
       <c r="G33">
-        <v>0.2604417974360282</v>
+        <v>0.2604417974360317</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>-0.520243399167454</v>
+        <v>-0.5202433991674514</v>
       </c>
       <c r="D34">
-        <v>-1.254125769840428</v>
+        <v>-1.25412576984043</v>
       </c>
       <c r="E34">
-        <v>0.9277717029035808</v>
+        <v>0.9277717029035778</v>
       </c>
       <c r="F34">
-        <v>0.02777640954934502</v>
+        <v>0.0277764095493449</v>
       </c>
       <c r="G34">
-        <v>-0.08057315988801712</v>
+        <v>-0.080573159888018</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.6765629736638851</v>
+        <v>0.6765629736638892</v>
       </c>
       <c r="D35">
-        <v>-2.046236414306992</v>
+        <v>-2.046236414306993</v>
       </c>
       <c r="E35">
-        <v>0.7405442632588647</v>
+        <v>0.7405442632588612</v>
       </c>
       <c r="F35">
-        <v>-1.239224608671641</v>
+        <v>-1.239224608671637</v>
       </c>
       <c r="G35">
-        <v>-0.8069629545780856</v>
+        <v>-0.8069629545780905</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.4455965048824831</v>
+        <v>-0.4455965048824828</v>
       </c>
       <c r="D36">
-        <v>0.2288971188780511</v>
+        <v>0.2288971188780496</v>
       </c>
       <c r="E36">
-        <v>0.1408595489319605</v>
+        <v>0.1408595489319603</v>
       </c>
       <c r="F36">
-        <v>0.06511139982558005</v>
+        <v>0.0651113998255813</v>
       </c>
       <c r="G36">
-        <v>-0.7479388715899876</v>
+        <v>-0.7479388715899874</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.5448877500572766</v>
+        <v>0.5448877500572753</v>
       </c>
       <c r="D37">
-        <v>-0.2810745375751035</v>
+        <v>-0.2810745375751047</v>
       </c>
       <c r="E37">
-        <v>0.7637133093436492</v>
+        <v>0.7637133093436479</v>
       </c>
       <c r="F37">
-        <v>0.2307747921873546</v>
+        <v>0.2307747921873576</v>
       </c>
       <c r="G37">
-        <v>-0.4636298481510794</v>
+        <v>-0.4636298481510788</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>-1.725318094471455</v>
+        <v>-1.725318094471451</v>
       </c>
       <c r="D38">
-        <v>-2.151277387110376</v>
+        <v>-2.151277387110373</v>
       </c>
       <c r="E38">
         <v>-2.104258094412891</v>
       </c>
       <c r="F38">
-        <v>-0.3392393225885617</v>
+        <v>-0.33923932258856</v>
       </c>
       <c r="G38">
-        <v>1.292029015729197</v>
+        <v>1.292029015729198</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.4175853010914498</v>
+        <v>-0.417585301091446</v>
       </c>
       <c r="D39">
-        <v>-1.683218986383815</v>
+        <v>-1.683218986383817</v>
       </c>
       <c r="E39">
-        <v>0.2041087542238036</v>
+        <v>0.204108754223801</v>
       </c>
       <c r="F39">
-        <v>0.04382423412519446</v>
+        <v>0.04382423412519751</v>
       </c>
       <c r="G39">
-        <v>-0.9845856453392851</v>
+        <v>-0.9845856453392852</v>
       </c>
     </row>
     <row r="40">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>-2.020004127682029</v>
+        <v>-2.02000412768203</v>
       </c>
       <c r="D40">
-        <v>0.6940683453609489</v>
+        <v>0.6940683453609429</v>
       </c>
       <c r="E40">
-        <v>1.923428359427721</v>
+        <v>1.923428359427717</v>
       </c>
       <c r="F40">
-        <v>-2.169515527507132</v>
+        <v>-2.169515527507133</v>
       </c>
       <c r="G40">
-        <v>0.4168483051066035</v>
+        <v>0.4168483051066022</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>-1.095028382172128</v>
+        <v>-1.09502838217213</v>
       </c>
       <c r="D41">
         <v>1.136597210390883</v>
       </c>
       <c r="E41">
-        <v>-1.3302407201602</v>
+        <v>-1.330240720160198</v>
       </c>
       <c r="F41">
-        <v>-0.1628396684769139</v>
+        <v>-0.162839668476914</v>
       </c>
       <c r="G41">
-        <v>0.1623967236813276</v>
+        <v>0.1623967236813263</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.05343931869479287</v>
+        <v>0.05343931869479726</v>
       </c>
       <c r="D42">
-        <v>-2.121432483564647</v>
+        <v>-2.121432483564646</v>
       </c>
       <c r="E42">
-        <v>-0.009998917603971451</v>
+        <v>-0.009998917603973121</v>
       </c>
       <c r="F42">
-        <v>0.6315326360492403</v>
+        <v>0.6315326360492417</v>
       </c>
       <c r="G42">
-        <v>-0.4035716674601368</v>
+        <v>-0.4035716674601341</v>
       </c>
     </row>
     <row r="43">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>1.291587139783482</v>
+        <v>1.291587139783481</v>
       </c>
       <c r="D43">
-        <v>0.8516116654765931</v>
+        <v>0.8516116654765949</v>
       </c>
       <c r="E43">
-        <v>-1.038429066824935</v>
+        <v>-1.038429066824934</v>
       </c>
       <c r="F43">
-        <v>-0.4939446405766644</v>
+        <v>-0.4939446405766653</v>
       </c>
       <c r="G43">
-        <v>0.174878872865714</v>
+        <v>0.1748788728657124</v>
       </c>
     </row>
     <row r="44">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.8866818192557662</v>
+        <v>0.8866818192557716</v>
       </c>
       <c r="D44">
-        <v>-2.250188571118042</v>
+        <v>-2.250188571118035</v>
       </c>
       <c r="E44">
-        <v>-2.546876482709511</v>
+        <v>-2.546876482709509</v>
       </c>
       <c r="F44">
-        <v>-0.8642167942470492</v>
+        <v>-0.8642167942470516</v>
       </c>
       <c r="G44">
         <v>2.372621685578638</v>
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="C45">
-        <v>-1.708995611674596</v>
+        <v>-1.708995611674597</v>
       </c>
       <c r="D45">
-        <v>0.7913901849675025</v>
+        <v>0.7913901849675001</v>
       </c>
       <c r="E45">
-        <v>-0.8965314365000674</v>
+        <v>-0.8965314365000669</v>
       </c>
       <c r="F45">
-        <v>-1.046772237890368</v>
+        <v>-1.046772237890369</v>
       </c>
       <c r="G45">
         <v>0.4769948945976141</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>0.1671163312617025</v>
+        <v>0.1671163312617018</v>
       </c>
       <c r="D46">
-        <v>0.120053995257027</v>
+        <v>0.1200539952570248</v>
       </c>
       <c r="E46">
-        <v>-0.5495481478733499</v>
+        <v>-0.54954814787335</v>
       </c>
       <c r="F46">
-        <v>-0.9083466500392215</v>
+        <v>-0.908346650039217</v>
       </c>
       <c r="G46">
-        <v>-1.292459115843268</v>
+        <v>-1.292459115843266</v>
       </c>
     </row>
     <row r="47">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.9445596494046159</v>
+        <v>-0.9445596494046145</v>
       </c>
       <c r="D47">
-        <v>-0.6789083510488271</v>
+        <v>-0.6789083510488294</v>
       </c>
       <c r="E47">
-        <v>0.8625665423051803</v>
+        <v>0.8625665423051792</v>
       </c>
       <c r="F47">
-        <v>-0.311904455492999</v>
+        <v>-0.3119044554929982</v>
       </c>
       <c r="G47">
-        <v>0.07997977530556677</v>
+        <v>0.07997977530556657</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>-0.4357945683076525</v>
+        <v>-0.4357945683076491</v>
       </c>
       <c r="D48">
-        <v>-1.625133901868897</v>
+        <v>-1.625133901868898</v>
       </c>
       <c r="E48">
-        <v>1.158705684598547</v>
+        <v>1.158705684598544</v>
       </c>
       <c r="F48">
-        <v>0.8165057446279245</v>
+        <v>0.8165057446279242</v>
       </c>
       <c r="G48">
-        <v>-0.1129287437423754</v>
+        <v>-0.1129287437423753</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.9683573026969241</v>
+        <v>-0.9683573026969253</v>
       </c>
       <c r="D49">
-        <v>0.5071397461672037</v>
+        <v>0.507139746167207</v>
       </c>
       <c r="E49">
-        <v>-2.163747501144052</v>
+        <v>-2.163747501144047</v>
       </c>
       <c r="F49">
-        <v>1.306246196177189</v>
+        <v>1.306246196177187</v>
       </c>
       <c r="G49">
-        <v>1.470617139466025</v>
+        <v>1.470617139466032</v>
       </c>
     </row>
     <row r="50">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>5.305277722373502</v>
+        <v>5.305277722373494</v>
       </c>
       <c r="D50">
-        <v>2.75001740370098</v>
+        <v>2.750017403700984</v>
       </c>
       <c r="E50">
-        <v>-0.8592728136366956</v>
+        <v>-0.8592728136366925</v>
       </c>
       <c r="F50">
-        <v>-0.2694046665118071</v>
+        <v>-0.2694046665118069</v>
       </c>
       <c r="G50">
-        <v>0.4289084930271724</v>
+        <v>0.4289084930271683</v>
       </c>
     </row>
     <row r="51">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.1785257198491063</v>
+        <v>-0.1785257198491042</v>
       </c>
       <c r="D51">
-        <v>-0.8922453017603021</v>
+        <v>-0.8922453017603057</v>
       </c>
       <c r="E51">
-        <v>1.48788407511675</v>
+        <v>1.487884075116748</v>
       </c>
       <c r="F51">
-        <v>-0.6856086224859295</v>
+        <v>-0.685608622485926</v>
       </c>
       <c r="G51">
-        <v>-1.078426685701695</v>
+        <v>-1.078426685701697</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>-0.07267967050626292</v>
+        <v>-0.0726796705062609</v>
       </c>
       <c r="D52">
-        <v>-0.7729210583083836</v>
+        <v>-0.7729210583083801</v>
       </c>
       <c r="E52">
-        <v>-2.182272534703686</v>
+        <v>-2.182272534703683</v>
       </c>
       <c r="F52">
-        <v>0.3805744181911691</v>
+        <v>0.3805744181911701</v>
       </c>
       <c r="G52">
-        <v>0.4683515193710149</v>
+        <v>0.4683515193710162</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>-1.04333168213009</v>
+        <v>-1.043331682130093</v>
       </c>
       <c r="D53">
-        <v>1.060998590410797</v>
+        <v>1.060998590410792</v>
       </c>
       <c r="E53">
-        <v>0.7718327559291512</v>
+        <v>0.7718327559291513</v>
       </c>
       <c r="F53">
-        <v>-1.188132461984446</v>
+        <v>-1.188132461984444</v>
       </c>
       <c r="G53">
-        <v>0.2293132621285819</v>
+        <v>0.2293132621285798</v>
       </c>
     </row>
     <row r="54">
@@ -1810,16 +1810,16 @@
         <v>-1.253610648208666</v>
       </c>
       <c r="D54">
-        <v>-0.3874653030491643</v>
+        <v>-0.3874653030491638</v>
       </c>
       <c r="E54">
-        <v>0.3317179545968124</v>
+        <v>0.3317179545968133</v>
       </c>
       <c r="F54">
-        <v>1.663497820140834</v>
+        <v>1.663497820140832</v>
       </c>
       <c r="G54">
-        <v>0.5207947770926225</v>
+        <v>0.5207947770926245</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>-0.7985245456504976</v>
+        <v>-0.7985245456505013</v>
       </c>
       <c r="D55">
         <v>1.736501793184854</v>
       </c>
       <c r="E55">
-        <v>1.213717901199047</v>
+        <v>1.21371790119905</v>
       </c>
       <c r="F55">
-        <v>2.648262337007733</v>
+        <v>2.648262337007728</v>
       </c>
       <c r="G55">
-        <v>0.2664171419915292</v>
+        <v>0.2664171419915352</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>0.07448549248473529</v>
+        <v>0.07448549248473818</v>
       </c>
       <c r="D56">
-        <v>-1.258925888755102</v>
+        <v>-1.258925888755098</v>
       </c>
       <c r="E56">
         <v>-1.411700642778584</v>
       </c>
       <c r="F56">
-        <v>0.06005252817029694</v>
+        <v>0.06005252817029502</v>
       </c>
       <c r="G56">
-        <v>1.216224944611133</v>
+        <v>1.216224944611134</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.7956283755139694</v>
+        <v>0.7956283755139745</v>
       </c>
       <c r="D57">
-        <v>-2.66734074645598</v>
+        <v>-2.667340746455977</v>
       </c>
       <c r="E57">
-        <v>-0.09105727217954972</v>
+        <v>-0.09105727217955091</v>
       </c>
       <c r="F57">
-        <v>0.6796007022461344</v>
+        <v>0.679600702246136</v>
       </c>
       <c r="G57">
-        <v>0.1097819154631855</v>
+        <v>0.1097819154631897</v>
       </c>
     </row>
     <row r="58">
@@ -1918,16 +1918,16 @@
         <v>-1.100152617910448</v>
       </c>
       <c r="D58">
-        <v>0.3644702828966292</v>
+        <v>0.3644702828966246</v>
       </c>
       <c r="E58">
-        <v>-0.2306740836396766</v>
+        <v>-0.2306740836396811</v>
       </c>
       <c r="F58">
-        <v>-3.781201276884106</v>
+        <v>-3.781201276884109</v>
       </c>
       <c r="G58">
-        <v>0.4399375399515217</v>
+        <v>0.439937539951516</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.6761222045069708</v>
+        <v>0.6761222045069721</v>
       </c>
       <c r="D59">
-        <v>-0.5198829908310415</v>
+        <v>-0.5198829908310344</v>
       </c>
       <c r="E59">
-        <v>-6.538935066214286</v>
+        <v>-6.53893506621428</v>
       </c>
       <c r="F59">
-        <v>-1.749213135791651</v>
+        <v>-1.749213135791647</v>
       </c>
       <c r="G59">
-        <v>-0.01565672096280884</v>
+        <v>-0.01565672096280771</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.08904923045113157</v>
+        <v>0.08904923045113439</v>
       </c>
       <c r="D60">
-        <v>-1.357323641468563</v>
+        <v>-1.35732364146856</v>
       </c>
       <c r="E60">
-        <v>0.1409351069120563</v>
+        <v>0.1409351069120561</v>
       </c>
       <c r="F60">
-        <v>1.077103957528552</v>
+        <v>1.07710395752855</v>
       </c>
       <c r="G60">
-        <v>0.9489965503245992</v>
+        <v>0.9489965503246024</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-0.5489044771093595</v>
+        <v>-0.5489044771093622</v>
       </c>
       <c r="D61">
-        <v>1.698741031488833</v>
+        <v>1.698741031488831</v>
       </c>
       <c r="E61">
-        <v>0.02640720446665827</v>
+        <v>0.02640720446666057</v>
       </c>
       <c r="F61">
-        <v>-0.1841964463682574</v>
+        <v>-0.1841964463682582</v>
       </c>
       <c r="G61">
-        <v>0.2406483955087285</v>
+        <v>0.2406483955087291</v>
       </c>
     </row>
     <row r="62">
@@ -2023,16 +2023,16 @@
         </is>
       </c>
       <c r="C62">
-        <v>-0.939684913265692</v>
+        <v>-0.9396849132656919</v>
       </c>
       <c r="D62">
-        <v>-0.1132191634100835</v>
+        <v>-0.1132191634100863</v>
       </c>
       <c r="E62">
-        <v>1.261634865737476</v>
+        <v>1.261634865737475</v>
       </c>
       <c r="F62">
-        <v>0.6769195228724498</v>
+        <v>0.6769195228724511</v>
       </c>
       <c r="G62">
         <v>-0.5128129579741282</v>
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>-0.2353428259980414</v>
+        <v>-0.2353428259980402</v>
       </c>
       <c r="D63">
-        <v>0.5218755469430437</v>
+        <v>0.5218755469430442</v>
       </c>
       <c r="E63">
-        <v>0.9957595380251837</v>
+        <v>0.9957595380251825</v>
       </c>
       <c r="F63">
-        <v>-0.6186143584479734</v>
+        <v>-0.6186143584479828</v>
       </c>
       <c r="G63">
-        <v>2.519979477962607</v>
+        <v>2.519979477962605</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.1794841926632521</v>
+        <v>0.1794841926632543</v>
       </c>
       <c r="D64">
-        <v>-0.9896717037694492</v>
+        <v>-0.9896717037694498</v>
       </c>
       <c r="E64">
-        <v>1.680427416487837</v>
+        <v>1.680427416487835</v>
       </c>
       <c r="F64">
-        <v>0.380454168916938</v>
+        <v>0.3804541689169352</v>
       </c>
       <c r="G64">
-        <v>0.7017259728965586</v>
+        <v>0.7017259728965589</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>1.474824453795017</v>
+        <v>1.474824453795025</v>
       </c>
       <c r="D65">
-        <v>-3.844778472297259</v>
+        <v>-3.844778472297256</v>
       </c>
       <c r="E65">
-        <v>0.3984580368630575</v>
+        <v>0.3984580368630544</v>
       </c>
       <c r="F65">
-        <v>1.100273987813288</v>
+        <v>1.100273987813289</v>
       </c>
       <c r="G65">
-        <v>-0.5084296987876121</v>
+        <v>-0.5084296987876088</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.5478817042341696</v>
+        <v>0.54788170423417</v>
       </c>
       <c r="D66">
-        <v>-0.3349713816818808</v>
+        <v>-0.3349713816818806</v>
       </c>
       <c r="E66">
-        <v>-0.01871684345690017</v>
+        <v>-0.01871684345690035</v>
       </c>
       <c r="F66">
-        <v>0.752161926746455</v>
+        <v>0.7521619267464573</v>
       </c>
       <c r="G66">
-        <v>-0.7678140375685892</v>
+        <v>-0.767814037568589</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>-0.01655970041201992</v>
+        <v>-0.01655970041201631</v>
       </c>
       <c r="D67">
-        <v>-1.886283372479944</v>
+        <v>-1.886283372479943</v>
       </c>
       <c r="E67">
-        <v>0.2156791982420247</v>
+        <v>0.2156791982420236</v>
       </c>
       <c r="F67">
-        <v>0.6534635965584877</v>
+        <v>0.6534635965584883</v>
       </c>
       <c r="G67">
-        <v>0.1094200055956902</v>
+        <v>0.1094200055956919</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>-1.992786690928561</v>
+        <v>-1.992786690928562</v>
       </c>
       <c r="D68">
-        <v>0.4989742401468779</v>
+        <v>0.4989742401468722</v>
       </c>
       <c r="E68">
-        <v>1.736144403985236</v>
+        <v>1.736144403985233</v>
       </c>
       <c r="F68">
-        <v>-0.7677862147330159</v>
+        <v>-0.7677862147330174</v>
       </c>
       <c r="G68">
-        <v>0.2581722367596341</v>
+        <v>0.2581722367596339</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>-0.3380388359801966</v>
+        <v>-0.3380388359801959</v>
       </c>
       <c r="D69">
-        <v>-0.2241156260732641</v>
+        <v>-0.2241156260732665</v>
       </c>
       <c r="E69">
-        <v>0.9438681269536655</v>
+        <v>0.9438681269536643</v>
       </c>
       <c r="F69">
-        <v>1.039348490018238</v>
+        <v>1.03934849001824</v>
       </c>
       <c r="G69">
-        <v>-1.62310810082464</v>
+        <v>-1.623108100824641</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>0.947151568623434</v>
+        <v>0.9471515686234381</v>
       </c>
       <c r="D70">
-        <v>-1.709993336924298</v>
+        <v>-1.709993336924294</v>
       </c>
       <c r="E70">
-        <v>-0.5721771497705248</v>
+        <v>-0.5721771497705254</v>
       </c>
       <c r="F70">
-        <v>-0.04066583517122435</v>
+        <v>-0.0406658351712251</v>
       </c>
       <c r="G70">
-        <v>0.7520623557744698</v>
+        <v>0.7520623557744693</v>
       </c>
     </row>
     <row r="71">
@@ -2266,16 +2266,16 @@
         </is>
       </c>
       <c r="C71">
-        <v>-1.650539134665601</v>
+        <v>-1.650539134665603</v>
       </c>
       <c r="D71">
-        <v>0.7830904939737777</v>
+        <v>0.7830904939737738</v>
       </c>
       <c r="E71">
-        <v>0.6384630673109164</v>
+        <v>0.6384630673109171</v>
       </c>
       <c r="F71">
-        <v>0.9346684533667271</v>
+        <v>0.9346684533667289</v>
       </c>
       <c r="G71">
         <v>-1.033916949391772</v>
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>7.428830141037231</v>
+        <v>7.428830141037218</v>
       </c>
       <c r="D72">
-        <v>3.386274762115687</v>
+        <v>3.38627476211569</v>
       </c>
       <c r="E72">
-        <v>3.219641435377671</v>
+        <v>3.219641435377672</v>
       </c>
       <c r="F72">
-        <v>0.9863518442616267</v>
+        <v>0.9863518442616261</v>
       </c>
       <c r="G72">
-        <v>-0.09042398458683304</v>
+        <v>-0.09042398458683459</v>
       </c>
     </row>
     <row r="73">
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>6.699961471447011</v>
+        <v>6.699961471447004</v>
       </c>
       <c r="D73">
-        <v>0.9856373037707843</v>
+        <v>0.9856373037707892</v>
       </c>
       <c r="E73">
-        <v>-0.7438139974299203</v>
+        <v>-0.7438139974299169</v>
       </c>
       <c r="F73">
-        <v>0.8887298028085311</v>
+        <v>0.888729802808536</v>
       </c>
       <c r="G73">
-        <v>-1.126390679183177</v>
+        <v>-1.126390679183167</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>-1.090165870742503</v>
+        <v>-1.090165870742506</v>
       </c>
       <c r="D74">
-        <v>1.627921112856944</v>
+        <v>1.627921112856941</v>
       </c>
       <c r="E74">
-        <v>1.042511893223507</v>
+        <v>1.042511893223508</v>
       </c>
       <c r="F74">
-        <v>0.7082631854652773</v>
+        <v>0.7082631854652752</v>
       </c>
       <c r="G74">
-        <v>-0.1329796001988828</v>
+        <v>-0.1329796001988841</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>2.184909076184761</v>
+        <v>2.184909076184764</v>
       </c>
       <c r="D75">
-        <v>-1.499013032568094</v>
+        <v>-1.499013032568092</v>
       </c>
       <c r="E75">
-        <v>0.6787135408491878</v>
+        <v>0.6787135408491863</v>
       </c>
       <c r="F75">
-        <v>0.405952079326112</v>
+        <v>0.4059520793261125</v>
       </c>
       <c r="G75">
-        <v>-0.399383286350235</v>
+        <v>-0.3993832863502327</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>1.296928463757378</v>
+        <v>1.296928463757377</v>
       </c>
       <c r="D76">
         <v>0.6727158458456941</v>
       </c>
       <c r="E76">
-        <v>0.3034640527278937</v>
+        <v>0.3034640527278942</v>
       </c>
       <c r="F76">
-        <v>-0.2089842819860576</v>
+        <v>-0.2089842819860564</v>
       </c>
       <c r="G76">
-        <v>-0.1905068406984892</v>
+        <v>-0.1905068406984872</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>-0.700255901164353</v>
+        <v>-0.700255901164354</v>
       </c>
       <c r="D77">
-        <v>0.5286012979057658</v>
+        <v>0.5286012979057682</v>
       </c>
       <c r="E77">
-        <v>-1.399184135473591</v>
+        <v>-1.399184135473587</v>
       </c>
       <c r="F77">
-        <v>2.973622392074202</v>
+        <v>2.973622392074203</v>
       </c>
       <c r="G77">
-        <v>-0.8869125558022297</v>
+        <v>-0.8869125558022248</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.3392395761354255</v>
+        <v>0.3392395761354287</v>
       </c>
       <c r="D78">
-        <v>-1.673125614877536</v>
+        <v>-1.673125614877534</v>
       </c>
       <c r="E78">
-        <v>0.4923997270466074</v>
+        <v>0.4923997270466058</v>
       </c>
       <c r="F78">
-        <v>-0.1071903950833891</v>
+        <v>-0.1071903950833893</v>
       </c>
       <c r="G78">
-        <v>0.4759426656573729</v>
+        <v>0.4759426656573739</v>
       </c>
     </row>
     <row r="79">
@@ -2482,16 +2482,16 @@
         </is>
       </c>
       <c r="C79">
-        <v>0.04795232208502367</v>
+        <v>0.04795232208501754</v>
       </c>
       <c r="D79">
-        <v>1.924857131938823</v>
+        <v>1.924857131938817</v>
       </c>
       <c r="E79">
-        <v>0.1792656664902168</v>
+        <v>0.1792656664902177</v>
       </c>
       <c r="F79">
-        <v>-0.5162758791232421</v>
+        <v>-0.5162758791232346</v>
       </c>
       <c r="G79">
         <v>-2.337947354053046</v>
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>-1.789333762395018</v>
+        <v>-1.78933376239502</v>
       </c>
       <c r="D80">
-        <v>0.6156746202614106</v>
+        <v>0.6156746202614107</v>
       </c>
       <c r="E80">
-        <v>-0.8307166860442573</v>
+        <v>-0.830716686044253</v>
       </c>
       <c r="F80">
-        <v>2.413640876621593</v>
+        <v>2.413640876621594</v>
       </c>
       <c r="G80">
-        <v>-0.285524995137698</v>
+        <v>-0.2855249951376947</v>
       </c>
     </row>
     <row r="81">
@@ -2539,16 +2539,16 @@
         <v>0.1030609943710922</v>
       </c>
       <c r="D81">
-        <v>0.1456701974386877</v>
+        <v>0.1456701974386888</v>
       </c>
       <c r="E81">
-        <v>-0.3398829899828845</v>
+        <v>-0.3398829899828818</v>
       </c>
       <c r="F81">
-        <v>0.3184515923595802</v>
+        <v>0.3184515923595812</v>
       </c>
       <c r="G81">
-        <v>0.4775102277333178</v>
+        <v>0.4775102277333206</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>-0.06240241313051167</v>
+        <v>-0.06240241313051414</v>
       </c>
       <c r="D82">
-        <v>1.210258392445438</v>
+        <v>1.21025839244544</v>
       </c>
       <c r="E82">
-        <v>-1.307072662662188</v>
+        <v>-1.307072662662183</v>
       </c>
       <c r="F82">
-        <v>0.724173634272392</v>
+        <v>0.724173634272391</v>
       </c>
       <c r="G82">
-        <v>0.4603255201345853</v>
+        <v>0.4603255201345891</v>
       </c>
     </row>
     <row r="83">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="C83">
-        <v>0.4033354198753804</v>
+        <v>0.4033354198753826</v>
       </c>
       <c r="D83">
-        <v>-0.6500888252950717</v>
+        <v>-0.6500888252950721</v>
       </c>
       <c r="E83">
         <v>-1.368726413710342</v>
       </c>
       <c r="F83">
-        <v>-0.8566575303883677</v>
+        <v>-0.8566575303883617</v>
       </c>
       <c r="G83">
         <v>-1.989662406968093</v>
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>1.85495613692216</v>
+        <v>1.854956136922164</v>
       </c>
       <c r="D84">
-        <v>-1.970698997553072</v>
+        <v>-1.97069899755307</v>
       </c>
       <c r="E84">
-        <v>-0.4001643643749108</v>
+        <v>-0.4001643643749131</v>
       </c>
       <c r="F84">
-        <v>-0.7484077648423667</v>
+        <v>-0.7484077648423617</v>
       </c>
       <c r="G84">
-        <v>-1.191177608934576</v>
+        <v>-1.191177608934577</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>2.141495847200827</v>
+        <v>2.141495847200834</v>
       </c>
       <c r="D85">
-        <v>-3.532409742946286</v>
+        <v>-3.532409742946285</v>
       </c>
       <c r="E85">
-        <v>1.098087425642492</v>
+        <v>1.098087425642487</v>
       </c>
       <c r="F85">
-        <v>-0.3667052865368187</v>
+        <v>-0.366705286536818</v>
       </c>
       <c r="G85">
-        <v>-0.9544714809330943</v>
+        <v>-0.9544714809330958</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>1.476092176935996</v>
+        <v>1.476092176936001</v>
       </c>
       <c r="D86">
-        <v>-2.225583324141915</v>
+        <v>-2.225583324141912</v>
       </c>
       <c r="E86">
-        <v>0.522501190112786</v>
+        <v>0.5225011901127836</v>
       </c>
       <c r="F86">
-        <v>0.3402453656104903</v>
+        <v>0.3402453656104895</v>
       </c>
       <c r="G86">
-        <v>0.2340242356241107</v>
+        <v>0.2340242356241101</v>
       </c>
     </row>
     <row r="87">
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="C87">
-        <v>-0.8743828164917298</v>
+        <v>-0.8743828164917318</v>
       </c>
       <c r="D87">
-        <v>1.267746699525663</v>
+        <v>1.267746699525661</v>
       </c>
       <c r="E87">
-        <v>-1.329569761711133</v>
+        <v>-1.32956976171113</v>
       </c>
       <c r="F87">
-        <v>-0.479005149446262</v>
+        <v>-0.479005149446258</v>
       </c>
       <c r="G87">
-        <v>-1.263210023814224</v>
+        <v>-1.263210023814222</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>-0.3859641394331498</v>
+        <v>-0.3859641394331459</v>
       </c>
       <c r="D88">
         <v>-2.095923454712123</v>
       </c>
       <c r="E88">
-        <v>0.3872327697226294</v>
+        <v>0.3872327697226274</v>
       </c>
       <c r="F88">
         <v>1.083590917368032</v>
       </c>
       <c r="G88">
-        <v>0.009255733274155848</v>
+        <v>0.00925573327415804</v>
       </c>
     </row>
     <row r="89">
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>-0.3998964194403413</v>
+        <v>-0.3998964194403435</v>
       </c>
       <c r="D89">
-        <v>1.185554248275131</v>
+        <v>1.185554248275132</v>
       </c>
       <c r="E89">
-        <v>-1.601741367399767</v>
+        <v>-1.601741367399764</v>
       </c>
       <c r="F89">
-        <v>-0.04339872235593892</v>
+        <v>-0.04339872235593795</v>
       </c>
       <c r="G89">
-        <v>-0.3053024324926072</v>
+        <v>-0.3053024324926057</v>
       </c>
     </row>
     <row r="90">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C90">
-        <v>-1.024399867273135</v>
+        <v>-1.024399867273138</v>
       </c>
       <c r="D90">
-        <v>1.740418451211338</v>
+        <v>1.740418451211339</v>
       </c>
       <c r="E90">
-        <v>-2.808738603880727</v>
+        <v>-2.80873860388072</v>
       </c>
       <c r="F90">
-        <v>0.6471957021988823</v>
+        <v>0.6471957021988848</v>
       </c>
       <c r="G90">
-        <v>-0.8829935540708546</v>
+        <v>-0.8829935540708549</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.1361123078968351</v>
+        <v>0.1361123078968338</v>
       </c>
       <c r="D91">
-        <v>0.472125743166937</v>
+        <v>0.4721257431669362</v>
       </c>
       <c r="E91">
-        <v>0.7043042174676902</v>
+        <v>0.7043042174676888</v>
       </c>
       <c r="F91">
-        <v>0.5461484967592966</v>
+        <v>0.5461484967592949</v>
       </c>
       <c r="G91">
-        <v>0.3999121083667524</v>
+        <v>0.3999121083667502</v>
       </c>
     </row>
     <row r="92">
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C92">
-        <v>-1.435710779372039</v>
+        <v>-1.435710779372041</v>
       </c>
       <c r="D92">
-        <v>0.899651003618368</v>
+        <v>0.8996510036183648</v>
       </c>
       <c r="E92">
-        <v>0.2083208090725462</v>
+        <v>0.2083208090725482</v>
       </c>
       <c r="F92">
-        <v>0.5180326583396277</v>
+        <v>0.5180326583396322</v>
       </c>
       <c r="G92">
         <v>-1.472853478392808</v>
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>1.18274918530408</v>
+        <v>1.182749185304081</v>
       </c>
       <c r="D93">
-        <v>-0.7986427321937112</v>
+        <v>-0.7986427321937111</v>
       </c>
       <c r="E93">
-        <v>1.499600183628948</v>
+        <v>1.499600183628947</v>
       </c>
       <c r="F93">
-        <v>0.1877303472486709</v>
+        <v>0.187730347248671</v>
       </c>
       <c r="G93">
-        <v>0.2836297020765737</v>
+        <v>0.283629702076577</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>-2.918850615336208</v>
+        <v>-2.918850615336211</v>
       </c>
       <c r="D94">
-        <v>1.705977389753442</v>
+        <v>1.705977389753434</v>
       </c>
       <c r="E94">
-        <v>2.482825328216293</v>
+        <v>2.482825328216287</v>
       </c>
       <c r="F94">
-        <v>-3.317554139365322</v>
+        <v>-3.317554139365329</v>
       </c>
       <c r="G94">
-        <v>1.842910327414351</v>
+        <v>1.842910327414347</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>2.493614895021707</v>
+        <v>2.493614895021708</v>
       </c>
       <c r="D95">
-        <v>-0.1318031043343828</v>
+        <v>-0.13180310433438</v>
       </c>
       <c r="E95">
-        <v>-0.0342662904997784</v>
+        <v>-0.03426629049977703</v>
       </c>
       <c r="F95">
-        <v>-0.3864713894775118</v>
+        <v>-0.3864713894775116</v>
       </c>
       <c r="G95">
-        <v>-0.1314398429431238</v>
+        <v>-0.1314398429431217</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.2142417421684095</v>
+        <v>-0.2142417421684083</v>
       </c>
       <c r="D96">
-        <v>-0.5018284534035033</v>
+        <v>-0.5018284534035025</v>
       </c>
       <c r="E96">
-        <v>-0.9166871294862521</v>
+        <v>-0.9166871294862508</v>
       </c>
       <c r="F96">
-        <v>0.3211845858418158</v>
+        <v>0.321184585841819</v>
       </c>
       <c r="G96">
-        <v>-0.6356263124185101</v>
+        <v>-0.6356263124185093</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>0.1954891760086629</v>
+        <v>0.1954891760086676</v>
       </c>
       <c r="D97">
-        <v>-1.702193881933263</v>
+        <v>-1.702193881933264</v>
       </c>
       <c r="E97">
-        <v>1.765293457351647</v>
+        <v>1.765293457351641</v>
       </c>
       <c r="F97">
-        <v>-0.6223865823127738</v>
+        <v>-0.6223865823127765</v>
       </c>
       <c r="G97">
-        <v>0.4723313986309637</v>
+        <v>0.4723313986309601</v>
       </c>
     </row>
     <row r="98">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>0.01810874488608935</v>
+        <v>0.01810874488608955</v>
       </c>
       <c r="D98">
-        <v>-0.04758565541722304</v>
+        <v>-0.04758565541722363</v>
       </c>
       <c r="E98">
-        <v>1.196186637792688</v>
+        <v>1.196186637792687</v>
       </c>
       <c r="F98">
-        <v>-0.1485118000589987</v>
+        <v>-0.1485118000589996</v>
       </c>
       <c r="G98">
-        <v>0.7444429557214427</v>
+        <v>0.7444429557214425</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>-1.914202721576639</v>
+        <v>-1.914202721576638</v>
       </c>
       <c r="D99">
-        <v>-0.6218829466940936</v>
+        <v>-0.6218829466940966</v>
       </c>
       <c r="E99">
-        <v>1.226381826388254</v>
+        <v>1.226381826388251</v>
       </c>
       <c r="F99">
-        <v>0.4661604927433721</v>
+        <v>0.4661604927433709</v>
       </c>
       <c r="G99">
-        <v>0.3539630802747349</v>
+        <v>0.3539630802747337</v>
       </c>
     </row>
     <row r="100">
@@ -3052,16 +3052,16 @@
         <v>-1.240084108604693</v>
       </c>
       <c r="D100">
-        <v>0.1426270693200418</v>
+        <v>0.1426270693200385</v>
       </c>
       <c r="E100">
-        <v>0.749726000051069</v>
+        <v>0.7497260000510679</v>
       </c>
       <c r="F100">
-        <v>0.1735547462977785</v>
+        <v>0.1735547462977783</v>
       </c>
       <c r="G100">
-        <v>-0.3731189965251148</v>
+        <v>-0.3731189965251164</v>
       </c>
     </row>
     <row r="101">
@@ -3079,16 +3079,16 @@
         <v>-1.100136134122091</v>
       </c>
       <c r="D101">
-        <v>0.0971898551888554</v>
+        <v>0.09718985518885485</v>
       </c>
       <c r="E101">
-        <v>0.02147334552160988</v>
+        <v>0.02147334552161067</v>
       </c>
       <c r="F101">
-        <v>0.6803565152116026</v>
+        <v>0.6803565152116013</v>
       </c>
       <c r="G101">
-        <v>0.3940706391388515</v>
+        <v>0.3940706391388547</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>-2.22275368998815</v>
+        <v>-2.222753689988152</v>
       </c>
       <c r="D102">
-        <v>0.6980600456755396</v>
+        <v>0.698060045675537</v>
       </c>
       <c r="E102">
-        <v>0.3567894348066633</v>
+        <v>0.3567894348066636</v>
       </c>
       <c r="F102">
-        <v>0.6252795500737393</v>
+        <v>0.6252795500737356</v>
       </c>
       <c r="G102">
-        <v>0.9008861415052669</v>
+        <v>0.9008861415052685</v>
       </c>
     </row>
     <row r="103">
@@ -3130,16 +3130,16 @@
         </is>
       </c>
       <c r="C103">
-        <v>-0.259129399895212</v>
+        <v>-0.2591293998952097</v>
       </c>
       <c r="D103">
-        <v>-1.244102349868072</v>
+        <v>-1.244102349868071</v>
       </c>
       <c r="E103">
-        <v>-0.3035097975377855</v>
+        <v>-0.3035097975377871</v>
       </c>
       <c r="F103">
-        <v>-0.3634277363877541</v>
+        <v>-0.3634277363877558</v>
       </c>
       <c r="G103">
         <v>1.047881764559866</v>
@@ -3157,16 +3157,16 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.09998521091027579</v>
+        <v>0.09998521091027848</v>
       </c>
       <c r="D104">
-        <v>-1.071532697180943</v>
+        <v>-1.071532697180946</v>
       </c>
       <c r="E104">
-        <v>-0.4158176882926754</v>
+        <v>-0.4158176882926776</v>
       </c>
       <c r="F104">
-        <v>-2.245790538378707</v>
+        <v>-2.245790538378702</v>
       </c>
       <c r="G104">
         <v>-1.553463546088059</v>
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>-0.7694240909373403</v>
+        <v>-0.7694240909373377</v>
       </c>
       <c r="D105">
         <v>-1.450876261698934</v>
       </c>
       <c r="E105">
-        <v>1.08470155981365</v>
+        <v>1.084701559813648</v>
       </c>
       <c r="F105">
-        <v>0.5803151251005344</v>
+        <v>0.5803151251005343</v>
       </c>
       <c r="G105">
-        <v>0.4911041474100762</v>
+        <v>0.4911041474100764</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-0.1419603628794348</v>
+        <v>-0.1419603628794331</v>
       </c>
       <c r="D106">
-        <v>-0.471885338210789</v>
+        <v>-0.4718853382107897</v>
       </c>
       <c r="E106">
-        <v>-0.9275490708430205</v>
+        <v>-0.9275490708430207</v>
       </c>
       <c r="F106">
-        <v>-1.221295273142122</v>
+        <v>-1.221295273142118</v>
       </c>
       <c r="G106">
-        <v>-0.5290960074863813</v>
+        <v>-0.5290960074863821</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>-0.4117568500856281</v>
+        <v>-0.4117568500856273</v>
       </c>
       <c r="D107">
-        <v>-0.5015513803984886</v>
+        <v>-0.5015513803984903</v>
       </c>
       <c r="E107">
-        <v>1.224333491232627</v>
+        <v>1.224333491232625</v>
       </c>
       <c r="F107">
-        <v>0.0728490275247525</v>
+        <v>0.07284902752475242</v>
       </c>
       <c r="G107">
-        <v>0.1332973022374727</v>
+        <v>0.1332973022374718</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.9947179245736958</v>
+        <v>0.9947179245737008</v>
       </c>
       <c r="D108">
-        <v>-2.553730950838788</v>
+        <v>-2.553730950838784</v>
       </c>
       <c r="E108">
-        <v>-1.418037989064378</v>
+        <v>-1.418037989064377</v>
       </c>
       <c r="F108">
-        <v>0.08129071587512783</v>
+        <v>0.08129071587512887</v>
       </c>
       <c r="G108">
-        <v>0.3802203913967922</v>
+        <v>0.3802203913967954</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.2610135881381166</v>
+        <v>-0.2610135881381158</v>
       </c>
       <c r="D109">
-        <v>-0.6219345981435006</v>
+        <v>-0.6219345981435009</v>
       </c>
       <c r="E109">
-        <v>0.748883039432799</v>
+        <v>0.7488830394327982</v>
       </c>
       <c r="F109">
-        <v>-1.021489442954076</v>
+        <v>-1.021489442954078</v>
       </c>
       <c r="G109">
-        <v>1.528636116486758</v>
+        <v>1.528636116486757</v>
       </c>
     </row>
     <row r="110">
@@ -3319,16 +3319,16 @@
         </is>
       </c>
       <c r="C110">
-        <v>0.5576526398004925</v>
+        <v>0.5576526398004922</v>
       </c>
       <c r="D110">
-        <v>0.6201658132529804</v>
+        <v>0.6201658132529853</v>
       </c>
       <c r="E110">
-        <v>-2.190841082365106</v>
+        <v>-2.1908410823651</v>
       </c>
       <c r="F110">
-        <v>0.4530198613210327</v>
+        <v>0.4530198613210317</v>
       </c>
       <c r="G110">
         <v>1.072447625938899</v>
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="C111">
-        <v>-0.5241636296833196</v>
+        <v>-0.5241636296833214</v>
       </c>
       <c r="D111">
-        <v>0.6527211931706253</v>
+        <v>0.6527211931706298</v>
       </c>
       <c r="E111">
-        <v>-2.39539457287791</v>
+        <v>-2.395394572877902</v>
       </c>
       <c r="F111">
         <v>2.597501547767849</v>
       </c>
       <c r="G111">
-        <v>0.5713614254773435</v>
+        <v>0.5713614254773505</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>-0.4313749760802864</v>
+        <v>-0.4313749760802884</v>
       </c>
       <c r="D112">
-        <v>0.9869937428517453</v>
+        <v>0.9869937428517432</v>
       </c>
       <c r="E112">
-        <v>-0.4122615488053394</v>
+        <v>-0.4122615488053384</v>
       </c>
       <c r="F112">
-        <v>-0.03944565957433479</v>
+        <v>-0.03944565957433321</v>
       </c>
       <c r="G112">
-        <v>-0.6587386041833602</v>
+        <v>-0.6587386041833571</v>
       </c>
     </row>
     <row r="113">
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C113">
-        <v>0.4724336245834299</v>
+        <v>0.4724336245834275</v>
       </c>
       <c r="D113">
-        <v>1.070236566053414</v>
+        <v>1.070236566053411</v>
       </c>
       <c r="E113">
-        <v>1.687953990885941</v>
+        <v>1.68795399088594</v>
       </c>
       <c r="F113">
-        <v>-0.1373402272171245</v>
+        <v>-0.1373402272171226</v>
       </c>
       <c r="G113">
-        <v>-1.07534454705767</v>
+        <v>-1.075344547057671</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>1.049024365549825</v>
+        <v>1.049024365549824</v>
       </c>
       <c r="D114">
-        <v>-0.06022433981154653</v>
+        <v>-0.06022433981154835</v>
       </c>
       <c r="E114">
-        <v>0.7859731686804354</v>
+        <v>0.785973168680434</v>
       </c>
       <c r="F114">
-        <v>0.1915253505123186</v>
+        <v>0.1915253505123219</v>
       </c>
       <c r="G114">
-        <v>-1.23297931218951</v>
+        <v>-1.232979312189511</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>0.159463212259615</v>
+        <v>0.1594632122596147</v>
       </c>
       <c r="D115">
-        <v>0.2226114987229224</v>
+        <v>0.2226114987229217</v>
       </c>
       <c r="E115">
-        <v>-0.2530582319865901</v>
+        <v>-0.2530582319865889</v>
       </c>
       <c r="F115">
-        <v>-0.3376993023430672</v>
+        <v>-0.3376993023430638</v>
       </c>
       <c r="G115">
-        <v>-0.5919014005527068</v>
+        <v>-0.5919014005527045</v>
       </c>
     </row>
     <row r="116">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C116">
-        <v>0.5346590869687405</v>
+        <v>0.5346590869687399</v>
       </c>
       <c r="D116">
-        <v>0.4584531156910117</v>
+        <v>0.4584531156910133</v>
       </c>
       <c r="E116">
-        <v>-1.019827233632841</v>
+        <v>-1.019827233632838</v>
       </c>
       <c r="F116">
-        <v>0.4226583829589599</v>
+        <v>0.4226583829589613</v>
       </c>
       <c r="G116">
-        <v>-0.6823324839836534</v>
+        <v>-0.6823324839836526</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>0.4480622659043861</v>
+        <v>0.4480622659043852</v>
       </c>
       <c r="D117">
-        <v>1.355886192961068</v>
+        <v>1.355886192961066</v>
       </c>
       <c r="E117">
-        <v>-0.3559168597816026</v>
+        <v>-0.3559168597816024</v>
       </c>
       <c r="F117">
         <v>-2.455612781940493</v>
       </c>
       <c r="G117">
-        <v>-0.4421224339029436</v>
+        <v>-0.442122433902947</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>1.304698694835589</v>
+        <v>1.304698694835585</v>
       </c>
       <c r="D118">
         <v>4.000591487220285</v>
       </c>
       <c r="E118">
-        <v>-0.9222828217670307</v>
+        <v>-0.9222828217670261</v>
       </c>
       <c r="F118">
-        <v>-0.7209601667420793</v>
+        <v>-0.7209601667420876</v>
       </c>
       <c r="G118">
-        <v>1.283988018304472</v>
+        <v>1.283988018304465</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>0.4133070019650629</v>
+        <v>0.413307001965066</v>
       </c>
       <c r="D119">
         <v>-1.718329114431041</v>
       </c>
       <c r="E119">
-        <v>0.6753542280805503</v>
+        <v>0.675354228080548</v>
       </c>
       <c r="F119">
-        <v>-0.1676809288487096</v>
+        <v>-0.1676809288487065</v>
       </c>
       <c r="G119">
-        <v>-0.3344321125346742</v>
+        <v>-0.334432112534674</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>0.8497120862004552</v>
+        <v>0.8497120862004574</v>
       </c>
       <c r="D120">
         <v>-1.121441538392672</v>
       </c>
       <c r="E120">
-        <v>0.6880057968307197</v>
+        <v>0.6880057968307174</v>
       </c>
       <c r="F120">
         <v>-0.9078701603230597</v>
       </c>
       <c r="G120">
-        <v>0.04503789871415053</v>
+        <v>0.04503789871414901</v>
       </c>
     </row>
     <row r="121">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C121">
-        <v>6.398152769456887</v>
+        <v>6.398152769456882</v>
       </c>
       <c r="D121">
-        <v>3.628069063013986</v>
+        <v>3.628069063013993</v>
       </c>
       <c r="E121">
-        <v>1.603596200181749</v>
+        <v>1.603596200181755</v>
       </c>
       <c r="F121">
-        <v>0.5530084297455358</v>
+        <v>0.5530084297455244</v>
       </c>
       <c r="G121">
-        <v>2.323062495387101</v>
+        <v>2.323062495387105</v>
       </c>
     </row>
     <row r="122">
@@ -3646,16 +3646,16 @@
         <v>-1.210427234769128</v>
       </c>
       <c r="D122">
-        <v>0.1027703805083455</v>
+        <v>0.102770380508344</v>
       </c>
       <c r="E122">
-        <v>0.4174130698621476</v>
+        <v>0.4174130698621485</v>
       </c>
       <c r="F122">
-        <v>1.205208288411626</v>
+        <v>1.205208288411627</v>
       </c>
       <c r="G122">
-        <v>-0.437321299324965</v>
+        <v>-0.437321299324963</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>-0.06824396736404403</v>
+        <v>-0.0682439673640442</v>
       </c>
       <c r="D123">
-        <v>0.4657829845972925</v>
+        <v>0.4657829845972923</v>
       </c>
       <c r="E123">
-        <v>1.153291229562563</v>
+        <v>1.153291229562564</v>
       </c>
       <c r="F123">
-        <v>0.2766883775082546</v>
+        <v>0.2766883775082514</v>
       </c>
       <c r="G123">
-        <v>1.104971903025376</v>
+        <v>1.104971903025377</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>-1.190510999193</v>
+        <v>-1.190510999193002</v>
       </c>
       <c r="D124">
-        <v>0.7862878632225797</v>
+        <v>0.7862878632225773</v>
       </c>
       <c r="E124">
-        <v>0.1187745985778344</v>
+        <v>0.1187745985778352</v>
       </c>
       <c r="F124">
-        <v>0.009186854186408066</v>
+        <v>0.009186854186409021</v>
       </c>
       <c r="G124">
-        <v>-0.2187039208438262</v>
+        <v>-0.2187039208438253</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>0.9306293185794614</v>
+        <v>0.9306293185794589</v>
       </c>
       <c r="D125">
-        <v>1.045116960872172</v>
+        <v>1.045116960872171</v>
       </c>
       <c r="E125">
-        <v>-0.7727667984009859</v>
+        <v>-0.7727667984009841</v>
       </c>
       <c r="F125">
-        <v>-1.371058101885851</v>
+        <v>-1.371058101885847</v>
       </c>
       <c r="G125">
-        <v>-1.122265420219737</v>
+        <v>-1.122265420219738</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>1.515184120314198</v>
+        <v>1.515184120314201</v>
       </c>
       <c r="D126">
         <v>-1.115814444075894</v>
       </c>
       <c r="E126">
-        <v>0.3300955555646667</v>
+        <v>0.3300955555646655</v>
       </c>
       <c r="F126">
-        <v>-0.2696384871561777</v>
+        <v>-0.2696384871561758</v>
       </c>
       <c r="G126">
-        <v>-1.363137828538196</v>
+        <v>-1.363137828538193</v>
       </c>
     </row>
   </sheetData>
